--- a/rancangan-muatan-se2026-ppu.xlsx
+++ b/rancangan-muatan-se2026-ppu.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\SE2026\monitoring-se2026-ppu\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C0028C4-3F97-4D09-864E-0A0D9786A70F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{794265BE-6558-4BC4-96A6-BD3E0DDEFA93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{961625FE-ECBA-4020-82CE-3C81D8EE7F83}"/>
+    <workbookView xWindow="3312" yWindow="3312" windowWidth="17280" windowHeight="8880" xr2:uid="{961625FE-ECBA-4020-82CE-3C81D8EE7F83}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -6373,7 +6373,7 @@
   <dimension ref="A1:AD1043"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="11.109375" customWidth="1"/>
+    <col min="1" max="1" width="15.5546875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="12.5546875" customWidth="1"/>
     <col min="3" max="3" width="24" customWidth="1"/>
     <col min="4" max="4" width="20.33203125" customWidth="1"/>
@@ -6398,7 +6398,7 @@
     <col min="30" max="30" width="31" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30" ht="93.6">
+    <row r="1" spans="1:30" ht="16.8">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
